--- a/education_forms/035_lysosome_biology_quiz--education_forms.xlsx
+++ b/education_forms/035_lysosome_biology_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a_cellular_organelle',_'value':_'a_cellular_organelle'}</t>
+          <t>a_cellular_organelle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A cellular organelle', 'value': 'A cellular organelle'}</t>
+          <t>A cellular organelle</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_cell_membrane',_'value':_'a_cell_membrane'}</t>
+          <t>a_cell_membrane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A cell membrane', 'value': 'A cell membrane'}</t>
+          <t>A cell membrane</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'a_cellular_organelle_that_digests_and_recycles',_'value':_'a_cellular_organelle_that_digests_and_recycles'}</t>
+          <t>a_cellular_organelle_that_digests_and_recycles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'A cellular organelle that digests and recycles', 'value': 'A cellular organelle that digests and recycles'}</t>
+          <t>A cellular organelle that digests and recycles</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'proteins',_'value':_'proteins'}</t>
+          <t>proteins</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Proteins', 'value': 'Proteins'}</t>
+          <t>Proteins</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lipids',_'value':_'lipids'}</t>
+          <t>lipids</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lipids', 'value': 'Lipids'}</t>
+          <t>Lipids</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'endoplasmic_reticulum',_'value':_'endoplasmic_reticulum'}</t>
+          <t>endoplasmic_reticulum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Endoplasmic reticulum', 'value': 'Endoplasmic reticulum'}</t>
+          <t>Endoplasmic reticulum</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'golgi_apparatus',_'value':_'golgi_apparatus'}</t>
+          <t>golgi_apparatus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Golgi apparatus', 'value': 'Golgi apparatus'}</t>
+          <t>Golgi apparatus</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cell_recycling',_'value':_'cell_recycling'}</t>
+          <t>cell_recycling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cell recycling', 'value': 'Cell recycling'}</t>
+          <t>Cell recycling</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cell_digestion',_'value':_'cell_digestion'}</t>
+          <t>cell_digestion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cell digestion', 'value': 'Cell digestion'}</t>
+          <t>Cell digestion</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lysosome',_'value':_'lysosome'}</t>
+          <t>lysosome</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lysosome', 'value': 'Lysosome'}</t>
+          <t>Lysosome</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phagosome',_'value':_'phagosome'}</t>
+          <t>phagosome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phagosome', 'value': 'Phagosome'}</t>
+          <t>Phagosome</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lysosome_has_to_be_produced',_'value':_'lysosome_has_to_be_produced'}</t>
+          <t>lysosome_has_to_be_produced</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lysosome has to be produced', 'value': 'Lysosome has to be produced'}</t>
+          <t>Lysosome has to be produced</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lysosome_is_produced',_'value':_'lysosome_is_produced'}</t>
+          <t>lysosome_is_produced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lysosome is produced', 'value': 'Lysosome is produced'}</t>
+          <t>Lysosome is produced</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lysosome_is_located_near_the',_'value':_'lysosome_is_located_near_the'}</t>
+          <t>lysosome_is_located_near_the</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lysosome is located near the', 'value': 'Lysosome is located near the'}</t>
+          <t>Lysosome is located near the</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mitochondria',_'value':_'mitochondria'}</t>
+          <t>mitochondria</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mitochondria', 'value': 'Mitochondria'}</t>
+          <t>Mitochondria</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'endoplasmic_reticulum',_'value':_'endoplasmic_reticulum'}</t>
+          <t>endoplasmic_reticulum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Endoplasmic reticulum', 'value': 'Endoplasmic reticulum'}</t>
+          <t>Endoplasmic reticulum</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'autophagy',_'value':_'autophagy'}</t>
+          <t>autophagy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Autophagy', 'value': 'Autophagy'}</t>
+          <t>Autophagy</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phagocytosis',_'value':_'phagocytosis'}</t>
+          <t>phagocytosis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phagocytosis', 'value': 'Phagocytosis'}</t>
+          <t>Phagocytosis</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'immune_cells',_'value':_'immune_cells'}</t>
+          <t>immune_cells</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Immune cells', 'value': 'Immune cells'}</t>
+          <t>Immune cells</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'epithelial_cells',_'value':_'epithelial_cells'}</t>
+          <t>epithelial_cells</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Epithelial cells', 'value': 'Epithelial cells'}</t>
+          <t>Epithelial cells</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'classrooms',_'value':_'classrooms'}</t>
+          <t>classrooms</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Classrooms', 'value': 'Classrooms'}</t>
+          <t>Classrooms</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lab_training',_'value':_'lab_training'}</t>
+          <t>lab_training</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lab training', 'value': 'Lab training'}</t>
+          <t>Lab training</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fast_data_collection',_'value':_'fast_data_collection'}</t>
+          <t>fast_data_collection</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fast data collection', 'value': 'fast data collection'}</t>
+          <t>fast data collection</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'easy_data_review',_'value':_'easy_data_review'}</t>
+          <t>easy_data_review</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'easy data review', 'value': 'easy data review'}</t>
+          <t>easy data review</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fast_data_collection',_'value':_'fast_data_collection'}</t>
+          <t>fast_data_collection</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'fast data collection', 'value': 'fast data collection'}</t>
+          <t>fast data collection</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'easy_review_of_each_submission',_'value':_'easy_review_of_each_submission'}</t>
+          <t>easy_review_of_each_submission</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'easy review of each submission', 'value': 'easy review of each submission'}</t>
+          <t>easy review of each submission</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
